--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C695FBFD-9CD3-4DE2-B08D-680B92C10E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD28442D-93B7-45FF-9283-A71962843E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -469,43 +469,43 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1563,80 +1563,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="42" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="43"/>
-      <c r="AD1" s="43"/>
-      <c r="AE1" s="43"/>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="43"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
     </row>
     <row r="2" spans="1:33" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="42" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
     </row>
     <row r="3" spans="1:33" s="17" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="20"/>
@@ -1674,49 +1674,49 @@
       <c r="AG3" s="18"/>
     </row>
     <row r="4" spans="1:33" s="14" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="39"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="43"/>
     </row>
     <row r="5" spans="1:33" s="14" customFormat="1" ht="13.5" customHeight="1">
       <c r="A5" s="32"/>
-      <c r="B5" s="36"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="15">
         <v>1</v>
       </c>
@@ -2348,37 +2348,37 @@
     <row r="20" spans="1:33" ht="22.5" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-      <c r="AE20" s="31"/>
-      <c r="AF20" s="31"/>
-      <c r="AG20" s="31"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="34"/>
+      <c r="AE20" s="34"/>
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="34"/>
     </row>
     <row r="21" spans="1:33" ht="22.5" customHeight="1">
       <c r="B21" s="6"/>
@@ -2416,37 +2416,37 @@
     </row>
     <row r="22" spans="1:33" ht="22.5" customHeight="1">
       <c r="B22" s="6"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="33"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="31"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
     </row>
     <row r="23" spans="1:33" ht="22.5" customHeight="1">
       <c r="B23" s="6"/>
@@ -2487,7 +2487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="222" customHeight="1">
+    <row r="25" spans="1:33" ht="242.25" customHeight="1">
       <c r="B25" s="25"/>
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
@@ -2525,20 +2525,20 @@
     <row r="27" spans="1:33" ht="21" customHeight="1">
       <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
+      <c r="AC27" s="44"/>
+      <c r="AD27" s="37"/>
+      <c r="AE27" s="37"/>
+      <c r="AF27" s="37"/>
+      <c r="AG27" s="37"/>
     </row>
     <row r="28" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AC28" s="40" t="s">
+      <c r="AC28" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
+      <c r="AD28" s="37"/>
+      <c r="AE28" s="37"/>
+      <c r="AF28" s="37"/>
+      <c r="AG28" s="37"/>
     </row>
     <row r="29" spans="1:33" ht="7.5" customHeight="1">
       <c r="D29" s="4"/>
@@ -2551,6 +2551,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="AC27:AG27"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="V20:V21"/>
+    <mergeCell ref="AB20:AB21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="AE20:AE21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AG20:AG21"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="AC28:AG28"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="AC20:AC21"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="AD20:AD21"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="AB22:AB23"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="P22:P23"/>
@@ -2567,60 +2621,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="O20:O21"/>
-    <mergeCell ref="AC28:AG28"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="AE22:AE23"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="AC20:AC21"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="AD20:AD21"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="AB22:AB23"/>
-    <mergeCell ref="AD22:AD23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="V22:V23"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="AG20:AG21"/>
-    <mergeCell ref="AC27:AG27"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="V20:V21"/>
-    <mergeCell ref="AB20:AB21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="AE20:AE21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="W22:W23"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="X20:X21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD28442D-93B7-45FF-9283-A71962843E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE33F98-7123-4DE1-9B62-C449F91917A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -397,7 +397,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -456,12 +456,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,43 +463,46 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1563,80 +1560,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="29" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
     </row>
     <row r="2" spans="1:33" s="17" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="29" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
     </row>
     <row r="3" spans="1:33" s="17" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="20"/>
@@ -1677,46 +1674,46 @@
       <c r="A4" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="33" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="42"/>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="42"/>
-      <c r="AB4" s="42"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="42"/>
-      <c r="AE4" s="42"/>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="43"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="37"/>
     </row>
     <row r="5" spans="1:33" s="14" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="15">
         <v>1</v>
       </c>
@@ -1818,37 +1815,37 @@
       <c r="B6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
     </row>
     <row r="7" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="13">
@@ -1857,37 +1854,37 @@
       <c r="B7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
     </row>
     <row r="8" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="13">
@@ -1896,37 +1893,37 @@
       <c r="B8" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-      <c r="AC8" s="26"/>
-      <c r="AD8" s="26"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="24"/>
     </row>
     <row r="9" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="13">
@@ -1935,37 +1932,37 @@
       <c r="B9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
     </row>
     <row r="10" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A10" s="13">
@@ -1974,37 +1971,37 @@
       <c r="B10" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="26"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
     </row>
     <row r="11" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="13">
@@ -2013,37 +2010,37 @@
       <c r="B11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
-      <c r="Z11" s="26"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-      <c r="AC11" s="26"/>
-      <c r="AD11" s="26"/>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
+      <c r="AG11" s="24"/>
     </row>
     <row r="12" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="13">
@@ -2052,37 +2049,37 @@
       <c r="B12" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
-      <c r="AC12" s="26"/>
-      <c r="AD12" s="26"/>
-      <c r="AE12" s="26"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
     </row>
     <row r="13" spans="1:33" ht="15.75" customHeight="1">
       <c r="A13" s="13">
@@ -2091,37 +2088,37 @@
       <c r="B13" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
     </row>
     <row r="14" spans="1:33" ht="15.75" customHeight="1">
       <c r="A14" s="13">
@@ -2130,37 +2127,37 @@
       <c r="B14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="27"/>
-      <c r="AD14" s="27"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="27"/>
-      <c r="AG14" s="27"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
     </row>
     <row r="15" spans="1:33" ht="15.75" customHeight="1">
       <c r="A15" s="13">
@@ -2169,37 +2166,37 @@
       <c r="B15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="27"/>
-      <c r="AC15" s="27"/>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="27"/>
-      <c r="AF15" s="27"/>
-      <c r="AG15" s="27"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
     </row>
     <row r="16" spans="1:33" ht="15.75" customHeight="1">
       <c r="A16" s="13">
@@ -2208,37 +2205,37 @@
       <c r="B16" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="27"/>
-      <c r="AC16" s="27"/>
-      <c r="AD16" s="27"/>
-      <c r="AE16" s="27"/>
-      <c r="AF16" s="27"/>
-      <c r="AG16" s="27"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
     </row>
     <row r="17" spans="1:33" ht="15.75" customHeight="1">
       <c r="A17" s="13"/>
@@ -2348,71 +2345,71 @@
     <row r="20" spans="1:33" ht="22.5" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="38"/>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="38"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
-      <c r="AE20" s="34"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="34"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="29"/>
     </row>
     <row r="21" spans="1:33" ht="22.5" customHeight="1">
       <c r="B21" s="6"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="32"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="32"/>
-      <c r="AG21" s="32"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="30"/>
+      <c r="AB21" s="30"/>
+      <c r="AC21" s="30"/>
+      <c r="AD21" s="30"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="30"/>
     </row>
     <row r="22" spans="1:33" ht="22.5" customHeight="1">
       <c r="B22" s="6"/>
@@ -2438,9 +2435,9 @@
       <c r="V22" s="31"/>
       <c r="W22" s="31"/>
       <c r="X22" s="31"/>
-      <c r="Y22" s="41"/>
+      <c r="Y22" s="32"/>
       <c r="Z22" s="31"/>
-      <c r="AA22" s="41"/>
+      <c r="AA22" s="32"/>
       <c r="AB22" s="31"/>
       <c r="AC22" s="31"/>
       <c r="AD22" s="31"/>
@@ -2450,37 +2447,37 @@
     </row>
     <row r="23" spans="1:33" ht="22.5" customHeight="1">
       <c r="B23" s="6"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="32"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="32"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="30"/>
     </row>
     <row r="24" spans="1:33" ht="19.5" customHeight="1">
       <c r="B24" s="21" t="s">
@@ -2488,57 +2485,57 @@
       </c>
     </row>
     <row r="25" spans="1:33" ht="242.25" customHeight="1">
-      <c r="B25" s="25"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-      <c r="AD25" s="24"/>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="24"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
+      <c r="X25" s="43"/>
+      <c r="Y25" s="43"/>
+      <c r="Z25" s="43"/>
+      <c r="AA25" s="43"/>
+      <c r="AB25" s="43"/>
+      <c r="AC25" s="43"/>
+      <c r="AD25" s="43"/>
+      <c r="AE25" s="43"/>
+      <c r="AF25" s="43"/>
+      <c r="AG25" s="43"/>
     </row>
     <row r="26" spans="1:33" ht="23.25" customHeight="1"/>
     <row r="27" spans="1:33" ht="21" customHeight="1">
       <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
-      <c r="AC27" s="44"/>
-      <c r="AD27" s="37"/>
-      <c r="AE27" s="37"/>
-      <c r="AF27" s="37"/>
-      <c r="AG27" s="37"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="28"/>
+      <c r="AE27" s="28"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="28"/>
     </row>
     <row r="28" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AC28" s="36" t="s">
+      <c r="AC28" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="AD28" s="37"/>
-      <c r="AE28" s="37"/>
-      <c r="AF28" s="37"/>
-      <c r="AG28" s="37"/>
+      <c r="AD28" s="28"/>
+      <c r="AE28" s="28"/>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="28"/>
     </row>
     <row r="29" spans="1:33" ht="7.5" customHeight="1">
       <c r="D29" s="4"/>
@@ -2550,7 +2547,62 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="B25:AG25"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="AF20:AF21"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="AC28:AG28"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="AC20:AC21"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="AD20:AD21"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AG20:AG21"/>
     <mergeCell ref="AC27:AG27"/>
     <mergeCell ref="T20:T21"/>
     <mergeCell ref="V20:V21"/>
@@ -2567,60 +2619,6 @@
     <mergeCell ref="O22:O23"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="X20:X21"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="V22:V23"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="AG20:AG21"/>
-    <mergeCell ref="AD22:AD23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="AC28:AG28"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="AE22:AE23"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="AC20:AC21"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="AD20:AD21"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="AB22:AB23"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="AG22:AG23"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="AF20:AF21"/>
-    <mergeCell ref="AC22:AC23"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="AF22:AF23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="O20:O21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -1800,8 +1800,16 @@
       <c r="AB6" s="24" t="n"/>
       <c r="AC6" s="24" t="n"/>
       <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="24" t="n"/>
-      <c r="AF6" s="24" t="n"/>
+      <c r="AE6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="24" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="14">
@@ -1841,8 +1849,16 @@
       <c r="AB7" s="24" t="n"/>
       <c r="AC7" s="24" t="n"/>
       <c r="AD7" s="24" t="n"/>
-      <c r="AE7" s="24" t="n"/>
-      <c r="AF7" s="24" t="n"/>
+      <c r="AE7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="24" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="14">
@@ -1882,8 +1898,16 @@
       <c r="AB8" s="24" t="n"/>
       <c r="AC8" s="24" t="n"/>
       <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="24" t="n"/>
-      <c r="AF8" s="24" t="n"/>
+      <c r="AE8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="24" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="14">
@@ -1923,8 +1947,16 @@
       <c r="AB9" s="24" t="n"/>
       <c r="AC9" s="24" t="n"/>
       <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="24" t="n"/>
-      <c r="AF9" s="24" t="n"/>
+      <c r="AE9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="24" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="14">
@@ -1964,8 +1996,16 @@
       <c r="AB10" s="24" t="n"/>
       <c r="AC10" s="24" t="n"/>
       <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="24" t="n"/>
-      <c r="AF10" s="24" t="n"/>
+      <c r="AE10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="24" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="14">
@@ -2005,8 +2045,16 @@
       <c r="AB11" s="24" t="n"/>
       <c r="AC11" s="24" t="n"/>
       <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="24" t="n"/>
-      <c r="AF11" s="24" t="n"/>
+      <c r="AE11" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF11" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG11" s="24" t="n"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="14">
@@ -2046,8 +2094,16 @@
       <c r="AB12" s="24" t="n"/>
       <c r="AC12" s="24" t="n"/>
       <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="24" t="n"/>
-      <c r="AF12" s="24" t="n"/>
+      <c r="AE12" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF12" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AG12" s="24" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -2087,8 +2143,16 @@
       <c r="AB13" s="25" t="n"/>
       <c r="AC13" s="25" t="n"/>
       <c r="AD13" s="25" t="n"/>
-      <c r="AE13" s="25" t="n"/>
-      <c r="AF13" s="25" t="n"/>
+      <c r="AE13" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG13" s="25" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -2128,8 +2192,16 @@
       <c r="AB14" s="25" t="n"/>
       <c r="AC14" s="25" t="n"/>
       <c r="AD14" s="25" t="n"/>
-      <c r="AE14" s="25" t="n"/>
-      <c r="AF14" s="25" t="n"/>
+      <c r="AE14" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF14" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG14" s="25" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -2169,8 +2241,16 @@
       <c r="AB15" s="25" t="n"/>
       <c r="AC15" s="25" t="n"/>
       <c r="AD15" s="25" t="n"/>
-      <c r="AE15" s="25" t="n"/>
-      <c r="AF15" s="25" t="n"/>
+      <c r="AE15" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG15" s="25" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -2210,8 +2290,16 @@
       <c r="AB16" s="25" t="n"/>
       <c r="AC16" s="25" t="n"/>
       <c r="AD16" s="25" t="n"/>
-      <c r="AE16" s="25" t="n"/>
-      <c r="AF16" s="25" t="n"/>
+      <c r="AE16" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF16" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG16" s="25" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -2245,8 +2333,16 @@
       <c r="AB17" s="9" t="n"/>
       <c r="AC17" s="9" t="n"/>
       <c r="AD17" s="9" t="n"/>
-      <c r="AE17" s="9" t="n"/>
-      <c r="AF17" s="9" t="n"/>
+      <c r="AE17" s="39" t="inlineStr">
+        <is>
+          <t>พีรวิชญ์</t>
+        </is>
+      </c>
+      <c r="AF17" s="39" t="inlineStr">
+        <is>
+          <t>พีรวิชญ์</t>
+        </is>
+      </c>
       <c r="AG17" s="9" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -2389,7 +2485,7 @@
       <c r="AG21" s="30" t="n"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="B22" s="6" t="n"/>
+      <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
       <c r="E22" s="31" t="n"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -355,7 +355,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -461,6 +461,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1772,45 +1775,37 @@
           <t>Worm Spindle ก่อนเริมงาน ตรวจสอบความ ผิดปกติของชุด  Back gauge  และ Motor</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
-      <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n"/>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="24" t="n"/>
-      <c r="R6" s="24" t="n"/>
-      <c r="S6" s="24" t="n"/>
-      <c r="T6" s="24" t="n"/>
-      <c r="U6" s="24" t="n"/>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="24" t="n"/>
-      <c r="X6" s="24" t="n"/>
-      <c r="Y6" s="24" t="n"/>
-      <c r="Z6" s="24" t="n"/>
-      <c r="AA6" s="24" t="n"/>
-      <c r="AB6" s="24" t="n"/>
-      <c r="AC6" s="24" t="n"/>
-      <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="24" t="n"/>
+      <c r="C6" s="24" t="inlineStr"/>
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="E6" s="24" t="inlineStr"/>
+      <c r="F6" s="24" t="inlineStr"/>
+      <c r="G6" s="24" t="inlineStr"/>
+      <c r="H6" s="24" t="inlineStr"/>
+      <c r="I6" s="24" t="inlineStr"/>
+      <c r="J6" s="24" t="inlineStr"/>
+      <c r="K6" s="24" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr"/>
+      <c r="M6" s="24" t="inlineStr"/>
+      <c r="N6" s="24" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr"/>
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="24" t="inlineStr"/>
+      <c r="R6" s="24" t="inlineStr"/>
+      <c r="S6" s="24" t="inlineStr"/>
+      <c r="T6" s="24" t="inlineStr"/>
+      <c r="U6" s="24" t="inlineStr"/>
+      <c r="V6" s="24" t="inlineStr"/>
+      <c r="W6" s="24" t="inlineStr"/>
+      <c r="X6" s="24" t="inlineStr"/>
+      <c r="Y6" s="24" t="inlineStr"/>
+      <c r="Z6" s="24" t="inlineStr"/>
+      <c r="AA6" s="24" t="inlineStr"/>
+      <c r="AB6" s="24" t="inlineStr"/>
+      <c r="AC6" s="24" t="inlineStr"/>
+      <c r="AD6" s="24" t="inlineStr"/>
+      <c r="AE6" s="24" t="inlineStr"/>
+      <c r="AF6" s="24" t="inlineStr"/>
+      <c r="AG6" s="24" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="14">
       <c r="A7" s="13" t="n">
@@ -1821,45 +1816,37 @@
           <t>เช็ค Auto  Up-Down back gauge  และ Manual ( ความคร่องตัวในการเคลื่อนที่ของ Spindle )</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
-      <c r="O7" s="24" t="n"/>
-      <c r="P7" s="24" t="n"/>
-      <c r="Q7" s="24" t="n"/>
-      <c r="R7" s="24" t="n"/>
-      <c r="S7" s="24" t="n"/>
-      <c r="T7" s="24" t="n"/>
-      <c r="U7" s="24" t="n"/>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="24" t="n"/>
-      <c r="X7" s="24" t="n"/>
-      <c r="Y7" s="24" t="n"/>
-      <c r="Z7" s="24" t="n"/>
-      <c r="AA7" s="24" t="n"/>
-      <c r="AB7" s="24" t="n"/>
-      <c r="AC7" s="24" t="n"/>
-      <c r="AD7" s="24" t="n"/>
-      <c r="AE7" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="24" t="n"/>
+      <c r="C7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr"/>
+      <c r="E7" s="24" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr"/>
+      <c r="G7" s="24" t="inlineStr"/>
+      <c r="H7" s="24" t="inlineStr"/>
+      <c r="I7" s="24" t="inlineStr"/>
+      <c r="J7" s="24" t="inlineStr"/>
+      <c r="K7" s="24" t="inlineStr"/>
+      <c r="L7" s="24" t="inlineStr"/>
+      <c r="M7" s="24" t="inlineStr"/>
+      <c r="N7" s="24" t="inlineStr"/>
+      <c r="O7" s="24" t="inlineStr"/>
+      <c r="P7" s="24" t="inlineStr"/>
+      <c r="Q7" s="24" t="inlineStr"/>
+      <c r="R7" s="24" t="inlineStr"/>
+      <c r="S7" s="24" t="inlineStr"/>
+      <c r="T7" s="24" t="inlineStr"/>
+      <c r="U7" s="24" t="inlineStr"/>
+      <c r="V7" s="24" t="inlineStr"/>
+      <c r="W7" s="24" t="inlineStr"/>
+      <c r="X7" s="24" t="inlineStr"/>
+      <c r="Y7" s="24" t="inlineStr"/>
+      <c r="Z7" s="24" t="inlineStr"/>
+      <c r="AA7" s="24" t="inlineStr"/>
+      <c r="AB7" s="24" t="inlineStr"/>
+      <c r="AC7" s="24" t="inlineStr"/>
+      <c r="AD7" s="24" t="inlineStr"/>
+      <c r="AE7" s="24" t="inlineStr"/>
+      <c r="AF7" s="24" t="inlineStr"/>
+      <c r="AG7" s="24" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="14">
       <c r="A8" s="13" t="n">
@@ -1870,45 +1857,37 @@
           <t>ตรวจสอบการ SLIDE  ของแกน X</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
-      <c r="O8" s="24" t="n"/>
-      <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="24" t="n"/>
-      <c r="R8" s="24" t="n"/>
-      <c r="S8" s="24" t="n"/>
-      <c r="T8" s="24" t="n"/>
-      <c r="U8" s="24" t="n"/>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="24" t="n"/>
-      <c r="X8" s="24" t="n"/>
-      <c r="Y8" s="24" t="n"/>
-      <c r="Z8" s="24" t="n"/>
-      <c r="AA8" s="24" t="n"/>
-      <c r="AB8" s="24" t="n"/>
-      <c r="AC8" s="24" t="n"/>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="n"/>
+      <c r="C8" s="24" t="inlineStr"/>
+      <c r="D8" s="24" t="inlineStr"/>
+      <c r="E8" s="24" t="inlineStr"/>
+      <c r="F8" s="24" t="inlineStr"/>
+      <c r="G8" s="24" t="inlineStr"/>
+      <c r="H8" s="24" t="inlineStr"/>
+      <c r="I8" s="24" t="inlineStr"/>
+      <c r="J8" s="24" t="inlineStr"/>
+      <c r="K8" s="24" t="inlineStr"/>
+      <c r="L8" s="24" t="inlineStr"/>
+      <c r="M8" s="24" t="inlineStr"/>
+      <c r="N8" s="24" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr"/>
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="24" t="inlineStr"/>
+      <c r="R8" s="24" t="inlineStr"/>
+      <c r="S8" s="24" t="inlineStr"/>
+      <c r="T8" s="24" t="inlineStr"/>
+      <c r="U8" s="24" t="inlineStr"/>
+      <c r="V8" s="24" t="inlineStr"/>
+      <c r="W8" s="24" t="inlineStr"/>
+      <c r="X8" s="24" t="inlineStr"/>
+      <c r="Y8" s="24" t="inlineStr"/>
+      <c r="Z8" s="24" t="inlineStr"/>
+      <c r="AA8" s="24" t="inlineStr"/>
+      <c r="AB8" s="24" t="inlineStr"/>
+      <c r="AC8" s="24" t="inlineStr"/>
+      <c r="AD8" s="24" t="inlineStr"/>
+      <c r="AE8" s="24" t="inlineStr"/>
+      <c r="AF8" s="24" t="inlineStr"/>
+      <c r="AG8" s="24" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="14">
       <c r="A9" s="13" t="n">
@@ -1919,45 +1898,37 @@
           <t>ตรวจสอบการ SLIDE  ของแกน Y</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="24" t="n"/>
-      <c r="K9" s="24" t="n"/>
-      <c r="L9" s="24" t="n"/>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="24" t="n"/>
-      <c r="O9" s="24" t="n"/>
-      <c r="P9" s="24" t="n"/>
-      <c r="Q9" s="24" t="n"/>
-      <c r="R9" s="24" t="n"/>
-      <c r="S9" s="24" t="n"/>
-      <c r="T9" s="24" t="n"/>
-      <c r="U9" s="24" t="n"/>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="24" t="n"/>
-      <c r="X9" s="24" t="n"/>
-      <c r="Y9" s="24" t="n"/>
-      <c r="Z9" s="24" t="n"/>
-      <c r="AA9" s="24" t="n"/>
-      <c r="AB9" s="24" t="n"/>
-      <c r="AC9" s="24" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="n"/>
+      <c r="C9" s="24" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="E9" s="24" t="inlineStr"/>
+      <c r="F9" s="24" t="inlineStr"/>
+      <c r="G9" s="24" t="inlineStr"/>
+      <c r="H9" s="24" t="inlineStr"/>
+      <c r="I9" s="24" t="inlineStr"/>
+      <c r="J9" s="24" t="inlineStr"/>
+      <c r="K9" s="24" t="inlineStr"/>
+      <c r="L9" s="24" t="inlineStr"/>
+      <c r="M9" s="24" t="inlineStr"/>
+      <c r="N9" s="24" t="inlineStr"/>
+      <c r="O9" s="24" t="inlineStr"/>
+      <c r="P9" s="24" t="inlineStr"/>
+      <c r="Q9" s="24" t="inlineStr"/>
+      <c r="R9" s="24" t="inlineStr"/>
+      <c r="S9" s="24" t="inlineStr"/>
+      <c r="T9" s="24" t="inlineStr"/>
+      <c r="U9" s="24" t="inlineStr"/>
+      <c r="V9" s="24" t="inlineStr"/>
+      <c r="W9" s="24" t="inlineStr"/>
+      <c r="X9" s="24" t="inlineStr"/>
+      <c r="Y9" s="24" t="inlineStr"/>
+      <c r="Z9" s="24" t="inlineStr"/>
+      <c r="AA9" s="24" t="inlineStr"/>
+      <c r="AB9" s="24" t="inlineStr"/>
+      <c r="AC9" s="24" t="inlineStr"/>
+      <c r="AD9" s="24" t="inlineStr"/>
+      <c r="AE9" s="24" t="inlineStr"/>
+      <c r="AF9" s="24" t="inlineStr"/>
+      <c r="AG9" s="24" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="14">
       <c r="A10" s="13" t="n">
@@ -1968,45 +1939,37 @@
           <t>ตรวจสอบการ SLIDE  ของแกน Z</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="24" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="24" t="n"/>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="24" t="n"/>
-      <c r="O10" s="24" t="n"/>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="24" t="n"/>
-      <c r="R10" s="24" t="n"/>
-      <c r="S10" s="24" t="n"/>
-      <c r="T10" s="24" t="n"/>
-      <c r="U10" s="24" t="n"/>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="24" t="n"/>
-      <c r="X10" s="24" t="n"/>
-      <c r="Y10" s="24" t="n"/>
-      <c r="Z10" s="24" t="n"/>
-      <c r="AA10" s="24" t="n"/>
-      <c r="AB10" s="24" t="n"/>
-      <c r="AC10" s="24" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="n"/>
+      <c r="C10" s="24" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="E10" s="24" t="inlineStr"/>
+      <c r="F10" s="24" t="inlineStr"/>
+      <c r="G10" s="24" t="inlineStr"/>
+      <c r="H10" s="24" t="inlineStr"/>
+      <c r="I10" s="24" t="inlineStr"/>
+      <c r="J10" s="24" t="inlineStr"/>
+      <c r="K10" s="24" t="inlineStr"/>
+      <c r="L10" s="24" t="inlineStr"/>
+      <c r="M10" s="24" t="inlineStr"/>
+      <c r="N10" s="24" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr"/>
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="24" t="inlineStr"/>
+      <c r="R10" s="24" t="inlineStr"/>
+      <c r="S10" s="24" t="inlineStr"/>
+      <c r="T10" s="24" t="inlineStr"/>
+      <c r="U10" s="24" t="inlineStr"/>
+      <c r="V10" s="24" t="inlineStr"/>
+      <c r="W10" s="24" t="inlineStr"/>
+      <c r="X10" s="24" t="inlineStr"/>
+      <c r="Y10" s="24" t="inlineStr"/>
+      <c r="Z10" s="24" t="inlineStr"/>
+      <c r="AA10" s="24" t="inlineStr"/>
+      <c r="AB10" s="24" t="inlineStr"/>
+      <c r="AC10" s="24" t="inlineStr"/>
+      <c r="AD10" s="24" t="inlineStr"/>
+      <c r="AE10" s="24" t="inlineStr"/>
+      <c r="AF10" s="24" t="inlineStr"/>
+      <c r="AG10" s="24" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="14">
       <c r="A11" s="13" t="n">
@@ -2017,45 +1980,37 @@
           <t>ระดับน้ำมันไฮดรอลิค ตรวจสอบน้ำมันในปั้มน้ำมันหล่อ ลื่นแกน  X,Y,Z</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
-      <c r="O11" s="24" t="n"/>
-      <c r="P11" s="24" t="n"/>
-      <c r="Q11" s="24" t="n"/>
-      <c r="R11" s="24" t="n"/>
-      <c r="S11" s="24" t="n"/>
-      <c r="T11" s="24" t="n"/>
-      <c r="U11" s="24" t="n"/>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="24" t="n"/>
-      <c r="X11" s="24" t="n"/>
-      <c r="Y11" s="24" t="n"/>
-      <c r="Z11" s="24" t="n"/>
-      <c r="AA11" s="24" t="n"/>
-      <c r="AB11" s="24" t="n"/>
-      <c r="AC11" s="24" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="n"/>
+      <c r="C11" s="24" t="inlineStr"/>
+      <c r="D11" s="24" t="inlineStr"/>
+      <c r="E11" s="24" t="inlineStr"/>
+      <c r="F11" s="24" t="inlineStr"/>
+      <c r="G11" s="24" t="inlineStr"/>
+      <c r="H11" s="24" t="inlineStr"/>
+      <c r="I11" s="24" t="inlineStr"/>
+      <c r="J11" s="24" t="inlineStr"/>
+      <c r="K11" s="24" t="inlineStr"/>
+      <c r="L11" s="24" t="inlineStr"/>
+      <c r="M11" s="24" t="inlineStr"/>
+      <c r="N11" s="24" t="inlineStr"/>
+      <c r="O11" s="24" t="inlineStr"/>
+      <c r="P11" s="24" t="inlineStr"/>
+      <c r="Q11" s="24" t="inlineStr"/>
+      <c r="R11" s="24" t="inlineStr"/>
+      <c r="S11" s="24" t="inlineStr"/>
+      <c r="T11" s="24" t="inlineStr"/>
+      <c r="U11" s="24" t="inlineStr"/>
+      <c r="V11" s="24" t="inlineStr"/>
+      <c r="W11" s="24" t="inlineStr"/>
+      <c r="X11" s="24" t="inlineStr"/>
+      <c r="Y11" s="24" t="inlineStr"/>
+      <c r="Z11" s="24" t="inlineStr"/>
+      <c r="AA11" s="24" t="inlineStr"/>
+      <c r="AB11" s="24" t="inlineStr"/>
+      <c r="AC11" s="24" t="inlineStr"/>
+      <c r="AD11" s="24" t="inlineStr"/>
+      <c r="AE11" s="24" t="inlineStr"/>
+      <c r="AF11" s="24" t="inlineStr"/>
+      <c r="AG11" s="24" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="14">
       <c r="A12" s="13" t="n">
@@ -2066,45 +2021,37 @@
           <t>ตรวจน้ำมันหล่อลื่นเย็น ตรวจสอบการทำงานของปั้ม COOLANT และสภาพของน้ำ  COOLANT</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n"/>
-      <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="24" t="n"/>
-      <c r="R12" s="24" t="n"/>
-      <c r="S12" s="24" t="n"/>
-      <c r="T12" s="24" t="n"/>
-      <c r="U12" s="24" t="n"/>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="24" t="n"/>
-      <c r="X12" s="24" t="n"/>
-      <c r="Y12" s="24" t="n"/>
-      <c r="Z12" s="24" t="n"/>
-      <c r="AA12" s="24" t="n"/>
-      <c r="AB12" s="24" t="n"/>
-      <c r="AC12" s="24" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF12" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="n"/>
+      <c r="C12" s="24" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr"/>
+      <c r="E12" s="24" t="inlineStr"/>
+      <c r="F12" s="24" t="inlineStr"/>
+      <c r="G12" s="24" t="inlineStr"/>
+      <c r="H12" s="24" t="inlineStr"/>
+      <c r="I12" s="24" t="inlineStr"/>
+      <c r="J12" s="24" t="inlineStr"/>
+      <c r="K12" s="24" t="inlineStr"/>
+      <c r="L12" s="24" t="inlineStr"/>
+      <c r="M12" s="24" t="inlineStr"/>
+      <c r="N12" s="24" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr"/>
+      <c r="P12" s="24" t="inlineStr"/>
+      <c r="Q12" s="24" t="inlineStr"/>
+      <c r="R12" s="24" t="inlineStr"/>
+      <c r="S12" s="24" t="inlineStr"/>
+      <c r="T12" s="24" t="inlineStr"/>
+      <c r="U12" s="24" t="inlineStr"/>
+      <c r="V12" s="24" t="inlineStr"/>
+      <c r="W12" s="24" t="inlineStr"/>
+      <c r="X12" s="24" t="inlineStr"/>
+      <c r="Y12" s="24" t="inlineStr"/>
+      <c r="Z12" s="24" t="inlineStr"/>
+      <c r="AA12" s="24" t="inlineStr"/>
+      <c r="AB12" s="24" t="inlineStr"/>
+      <c r="AC12" s="24" t="inlineStr"/>
+      <c r="AD12" s="24" t="inlineStr"/>
+      <c r="AE12" s="24" t="inlineStr"/>
+      <c r="AF12" s="24" t="inlineStr"/>
+      <c r="AG12" s="24" t="inlineStr"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="13" t="n">
@@ -2115,45 +2062,37 @@
           <t>ตรวจสอบหน้าจอ  DIGITAL READ OUT และการทำ งานของ LINEAR SCALE</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="25" t="n"/>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="25" t="n"/>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="25" t="n"/>
-      <c r="O13" s="25" t="n"/>
-      <c r="P13" s="25" t="n"/>
-      <c r="Q13" s="25" t="n"/>
-      <c r="R13" s="25" t="n"/>
-      <c r="S13" s="25" t="n"/>
-      <c r="T13" s="25" t="n"/>
-      <c r="U13" s="25" t="n"/>
-      <c r="V13" s="25" t="n"/>
-      <c r="W13" s="25" t="n"/>
-      <c r="X13" s="25" t="n"/>
-      <c r="Y13" s="26" t="n"/>
-      <c r="Z13" s="25" t="n"/>
-      <c r="AA13" s="26" t="n"/>
-      <c r="AB13" s="25" t="n"/>
-      <c r="AC13" s="25" t="n"/>
-      <c r="AD13" s="25" t="n"/>
-      <c r="AE13" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF13" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG13" s="25" t="n"/>
+      <c r="C13" s="25" t="inlineStr"/>
+      <c r="D13" s="25" t="inlineStr"/>
+      <c r="E13" s="25" t="inlineStr"/>
+      <c r="F13" s="25" t="inlineStr"/>
+      <c r="G13" s="25" t="inlineStr"/>
+      <c r="H13" s="25" t="inlineStr"/>
+      <c r="I13" s="25" t="inlineStr"/>
+      <c r="J13" s="25" t="inlineStr"/>
+      <c r="K13" s="25" t="inlineStr"/>
+      <c r="L13" s="25" t="inlineStr"/>
+      <c r="M13" s="25" t="inlineStr"/>
+      <c r="N13" s="25" t="inlineStr"/>
+      <c r="O13" s="25" t="inlineStr"/>
+      <c r="P13" s="25" t="inlineStr"/>
+      <c r="Q13" s="25" t="inlineStr"/>
+      <c r="R13" s="25" t="inlineStr"/>
+      <c r="S13" s="25" t="inlineStr"/>
+      <c r="T13" s="25" t="inlineStr"/>
+      <c r="U13" s="25" t="inlineStr"/>
+      <c r="V13" s="25" t="inlineStr"/>
+      <c r="W13" s="25" t="inlineStr"/>
+      <c r="X13" s="25" t="inlineStr"/>
+      <c r="Y13" s="26" t="inlineStr"/>
+      <c r="Z13" s="25" t="inlineStr"/>
+      <c r="AA13" s="26" t="inlineStr"/>
+      <c r="AB13" s="25" t="inlineStr"/>
+      <c r="AC13" s="25" t="inlineStr"/>
+      <c r="AD13" s="25" t="inlineStr"/>
+      <c r="AE13" s="26" t="inlineStr"/>
+      <c r="AF13" s="26" t="inlineStr"/>
+      <c r="AG13" s="25" t="inlineStr"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -2164,45 +2103,37 @@
           <t>หยอดน้ำมันหล่อลื่นทุกวันจันทร์</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="25" t="n"/>
-      <c r="O14" s="25" t="n"/>
-      <c r="P14" s="25" t="n"/>
-      <c r="Q14" s="25" t="n"/>
-      <c r="R14" s="25" t="n"/>
-      <c r="S14" s="25" t="n"/>
-      <c r="T14" s="25" t="n"/>
-      <c r="U14" s="25" t="n"/>
-      <c r="V14" s="25" t="n"/>
-      <c r="W14" s="25" t="n"/>
-      <c r="X14" s="25" t="n"/>
-      <c r="Y14" s="26" t="n"/>
-      <c r="Z14" s="25" t="n"/>
-      <c r="AA14" s="26" t="n"/>
-      <c r="AB14" s="25" t="n"/>
-      <c r="AC14" s="25" t="n"/>
-      <c r="AD14" s="25" t="n"/>
-      <c r="AE14" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF14" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG14" s="25" t="n"/>
+      <c r="C14" s="25" t="inlineStr"/>
+      <c r="D14" s="25" t="inlineStr"/>
+      <c r="E14" s="25" t="inlineStr"/>
+      <c r="F14" s="25" t="inlineStr"/>
+      <c r="G14" s="25" t="inlineStr"/>
+      <c r="H14" s="25" t="inlineStr"/>
+      <c r="I14" s="25" t="inlineStr"/>
+      <c r="J14" s="25" t="inlineStr"/>
+      <c r="K14" s="25" t="inlineStr"/>
+      <c r="L14" s="25" t="inlineStr"/>
+      <c r="M14" s="25" t="inlineStr"/>
+      <c r="N14" s="25" t="inlineStr"/>
+      <c r="O14" s="25" t="inlineStr"/>
+      <c r="P14" s="25" t="inlineStr"/>
+      <c r="Q14" s="25" t="inlineStr"/>
+      <c r="R14" s="25" t="inlineStr"/>
+      <c r="S14" s="25" t="inlineStr"/>
+      <c r="T14" s="25" t="inlineStr"/>
+      <c r="U14" s="25" t="inlineStr"/>
+      <c r="V14" s="25" t="inlineStr"/>
+      <c r="W14" s="25" t="inlineStr"/>
+      <c r="X14" s="25" t="inlineStr"/>
+      <c r="Y14" s="26" t="inlineStr"/>
+      <c r="Z14" s="25" t="inlineStr"/>
+      <c r="AA14" s="26" t="inlineStr"/>
+      <c r="AB14" s="25" t="inlineStr"/>
+      <c r="AC14" s="25" t="inlineStr"/>
+      <c r="AD14" s="25" t="inlineStr"/>
+      <c r="AE14" s="26" t="inlineStr"/>
+      <c r="AF14" s="26" t="inlineStr"/>
+      <c r="AG14" s="25" t="inlineStr"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="13" t="n">
@@ -2213,45 +2144,37 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าแสงสว่างของเครื่อง</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="25" t="n"/>
-      <c r="N15" s="25" t="n"/>
-      <c r="O15" s="25" t="n"/>
-      <c r="P15" s="25" t="n"/>
-      <c r="Q15" s="25" t="n"/>
-      <c r="R15" s="25" t="n"/>
-      <c r="S15" s="25" t="n"/>
-      <c r="T15" s="25" t="n"/>
-      <c r="U15" s="25" t="n"/>
-      <c r="V15" s="25" t="n"/>
-      <c r="W15" s="25" t="n"/>
-      <c r="X15" s="25" t="n"/>
-      <c r="Y15" s="26" t="n"/>
-      <c r="Z15" s="25" t="n"/>
-      <c r="AA15" s="26" t="n"/>
-      <c r="AB15" s="25" t="n"/>
-      <c r="AC15" s="25" t="n"/>
-      <c r="AD15" s="25" t="n"/>
-      <c r="AE15" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF15" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG15" s="25" t="n"/>
+      <c r="C15" s="25" t="inlineStr"/>
+      <c r="D15" s="25" t="inlineStr"/>
+      <c r="E15" s="25" t="inlineStr"/>
+      <c r="F15" s="25" t="inlineStr"/>
+      <c r="G15" s="25" t="inlineStr"/>
+      <c r="H15" s="25" t="inlineStr"/>
+      <c r="I15" s="25" t="inlineStr"/>
+      <c r="J15" s="25" t="inlineStr"/>
+      <c r="K15" s="25" t="inlineStr"/>
+      <c r="L15" s="25" t="inlineStr"/>
+      <c r="M15" s="25" t="inlineStr"/>
+      <c r="N15" s="25" t="inlineStr"/>
+      <c r="O15" s="25" t="inlineStr"/>
+      <c r="P15" s="25" t="inlineStr"/>
+      <c r="Q15" s="25" t="inlineStr"/>
+      <c r="R15" s="25" t="inlineStr"/>
+      <c r="S15" s="25" t="inlineStr"/>
+      <c r="T15" s="25" t="inlineStr"/>
+      <c r="U15" s="25" t="inlineStr"/>
+      <c r="V15" s="25" t="inlineStr"/>
+      <c r="W15" s="25" t="inlineStr"/>
+      <c r="X15" s="25" t="inlineStr"/>
+      <c r="Y15" s="26" t="inlineStr"/>
+      <c r="Z15" s="25" t="inlineStr"/>
+      <c r="AA15" s="26" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
+      <c r="AC15" s="25" t="inlineStr"/>
+      <c r="AD15" s="25" t="inlineStr"/>
+      <c r="AE15" s="26" t="inlineStr"/>
+      <c r="AF15" s="26" t="inlineStr"/>
+      <c r="AG15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="13" t="n">
@@ -2262,88 +2185,72 @@
           <t>ตรวจสอบสภาพความพร้อมโดยรวมของเครื่องจักร  และอุกรณ์เสริมต่าง ๆ</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="25" t="n"/>
-      <c r="O16" s="25" t="n"/>
-      <c r="P16" s="25" t="n"/>
-      <c r="Q16" s="25" t="n"/>
-      <c r="R16" s="25" t="n"/>
-      <c r="S16" s="25" t="n"/>
-      <c r="T16" s="25" t="n"/>
-      <c r="U16" s="25" t="n"/>
-      <c r="V16" s="25" t="n"/>
-      <c r="W16" s="25" t="n"/>
-      <c r="X16" s="25" t="n"/>
-      <c r="Y16" s="26" t="n"/>
-      <c r="Z16" s="25" t="n"/>
-      <c r="AA16" s="26" t="n"/>
-      <c r="AB16" s="25" t="n"/>
-      <c r="AC16" s="25" t="n"/>
-      <c r="AD16" s="25" t="n"/>
-      <c r="AE16" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF16" s="26" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG16" s="25" t="n"/>
+      <c r="C16" s="25" t="inlineStr"/>
+      <c r="D16" s="25" t="inlineStr"/>
+      <c r="E16" s="25" t="inlineStr"/>
+      <c r="F16" s="25" t="inlineStr"/>
+      <c r="G16" s="25" t="inlineStr"/>
+      <c r="H16" s="25" t="inlineStr"/>
+      <c r="I16" s="25" t="inlineStr"/>
+      <c r="J16" s="25" t="inlineStr"/>
+      <c r="K16" s="25" t="inlineStr"/>
+      <c r="L16" s="25" t="inlineStr"/>
+      <c r="M16" s="25" t="inlineStr"/>
+      <c r="N16" s="25" t="inlineStr"/>
+      <c r="O16" s="25" t="inlineStr"/>
+      <c r="P16" s="25" t="inlineStr"/>
+      <c r="Q16" s="25" t="inlineStr"/>
+      <c r="R16" s="25" t="inlineStr"/>
+      <c r="S16" s="25" t="inlineStr"/>
+      <c r="T16" s="25" t="inlineStr"/>
+      <c r="U16" s="25" t="inlineStr"/>
+      <c r="V16" s="25" t="inlineStr"/>
+      <c r="W16" s="25" t="inlineStr"/>
+      <c r="X16" s="25" t="inlineStr"/>
+      <c r="Y16" s="26" t="inlineStr"/>
+      <c r="Z16" s="25" t="inlineStr"/>
+      <c r="AA16" s="26" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
+      <c r="AC16" s="25" t="inlineStr"/>
+      <c r="AD16" s="25" t="inlineStr"/>
+      <c r="AE16" s="26" t="inlineStr"/>
+      <c r="AF16" s="26" t="inlineStr"/>
+      <c r="AG16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="12" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="9" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="9" t="n"/>
-      <c r="U17" s="9" t="n"/>
-      <c r="V17" s="9" t="n"/>
-      <c r="W17" s="9" t="n"/>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="9" t="n"/>
-      <c r="Z17" s="9" t="n"/>
-      <c r="AA17" s="9" t="n"/>
-      <c r="AB17" s="9" t="n"/>
-      <c r="AC17" s="9" t="n"/>
-      <c r="AD17" s="9" t="n"/>
-      <c r="AE17" s="39" t="inlineStr">
-        <is>
-          <t>พีรวิชญ์</t>
-        </is>
-      </c>
-      <c r="AF17" s="39" t="inlineStr">
-        <is>
-          <t>พีรวิชญ์</t>
-        </is>
-      </c>
-      <c r="AG17" s="9" t="n"/>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr"/>
+      <c r="N17" s="9" t="inlineStr"/>
+      <c r="O17" s="9" t="inlineStr"/>
+      <c r="P17" s="9" t="inlineStr"/>
+      <c r="Q17" s="9" t="inlineStr"/>
+      <c r="R17" s="9" t="inlineStr"/>
+      <c r="S17" s="9" t="inlineStr"/>
+      <c r="T17" s="9" t="inlineStr"/>
+      <c r="U17" s="9" t="inlineStr"/>
+      <c r="V17" s="9" t="inlineStr"/>
+      <c r="W17" s="9" t="inlineStr"/>
+      <c r="X17" s="9" t="inlineStr"/>
+      <c r="Y17" s="9" t="inlineStr"/>
+      <c r="Z17" s="9" t="inlineStr"/>
+      <c r="AA17" s="9" t="inlineStr"/>
+      <c r="AB17" s="9" t="inlineStr"/>
+      <c r="AC17" s="9" t="inlineStr"/>
+      <c r="AD17" s="9" t="inlineStr"/>
+      <c r="AE17" s="39" t="inlineStr"/>
+      <c r="AF17" s="39" t="inlineStr"/>
+      <c r="AG17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="13" t="n"/>
@@ -2383,37 +2290,37 @@
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="11" t="n"/>
       <c r="B19" s="10" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="9" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="9" t="n"/>
-      <c r="U19" s="9" t="n"/>
-      <c r="V19" s="9" t="n"/>
-      <c r="W19" s="9" t="n"/>
-      <c r="X19" s="9" t="n"/>
-      <c r="Y19" s="9" t="n"/>
-      <c r="Z19" s="9" t="n"/>
-      <c r="AA19" s="9" t="n"/>
-      <c r="AB19" s="9" t="n"/>
-      <c r="AC19" s="9" t="n"/>
-      <c r="AD19" s="9" t="n"/>
-      <c r="AE19" s="9" t="n"/>
-      <c r="AF19" s="9" t="n"/>
-      <c r="AG19" s="9" t="n"/>
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
+      <c r="M19" s="9" t="inlineStr"/>
+      <c r="N19" s="9" t="inlineStr"/>
+      <c r="O19" s="9" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr"/>
+      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="R19" s="9" t="inlineStr"/>
+      <c r="S19" s="9" t="inlineStr"/>
+      <c r="T19" s="9" t="inlineStr"/>
+      <c r="U19" s="9" t="inlineStr"/>
+      <c r="V19" s="9" t="inlineStr"/>
+      <c r="W19" s="9" t="inlineStr"/>
+      <c r="X19" s="9" t="inlineStr"/>
+      <c r="Y19" s="9" t="inlineStr"/>
+      <c r="Z19" s="9" t="inlineStr"/>
+      <c r="AA19" s="9" t="inlineStr"/>
+      <c r="AB19" s="9" t="inlineStr"/>
+      <c r="AC19" s="9" t="inlineStr"/>
+      <c r="AD19" s="9" t="inlineStr"/>
+      <c r="AE19" s="9" t="inlineStr"/>
+      <c r="AF19" s="9" t="inlineStr"/>
+      <c r="AG19" s="9" t="inlineStr"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="8" t="n"/>
@@ -2485,7 +2392,7 @@
       <c r="AG21" s="30" t="n"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="B22" s="6" t="inlineStr"/>
+      <c r="B22" s="44" t="inlineStr"/>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
       <c r="E22" s="31" t="n"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -1780,7 +1780,11 @@
       <c r="E6" s="24" t="inlineStr"/>
       <c r="F6" s="24" t="inlineStr"/>
       <c r="G6" s="24" t="inlineStr"/>
-      <c r="H6" s="24" t="inlineStr"/>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="24" t="inlineStr"/>
       <c r="J6" s="24" t="inlineStr"/>
       <c r="K6" s="24" t="inlineStr"/>
@@ -1821,7 +1825,11 @@
       <c r="E7" s="24" t="inlineStr"/>
       <c r="F7" s="24" t="inlineStr"/>
       <c r="G7" s="24" t="inlineStr"/>
-      <c r="H7" s="24" t="inlineStr"/>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="24" t="inlineStr"/>
       <c r="J7" s="24" t="inlineStr"/>
       <c r="K7" s="24" t="inlineStr"/>
@@ -1862,7 +1870,11 @@
       <c r="E8" s="24" t="inlineStr"/>
       <c r="F8" s="24" t="inlineStr"/>
       <c r="G8" s="24" t="inlineStr"/>
-      <c r="H8" s="24" t="inlineStr"/>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="24" t="inlineStr"/>
       <c r="J8" s="24" t="inlineStr"/>
       <c r="K8" s="24" t="inlineStr"/>
@@ -1903,7 +1915,11 @@
       <c r="E9" s="24" t="inlineStr"/>
       <c r="F9" s="24" t="inlineStr"/>
       <c r="G9" s="24" t="inlineStr"/>
-      <c r="H9" s="24" t="inlineStr"/>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="24" t="inlineStr"/>
       <c r="J9" s="24" t="inlineStr"/>
       <c r="K9" s="24" t="inlineStr"/>
@@ -1944,7 +1960,11 @@
       <c r="E10" s="24" t="inlineStr"/>
       <c r="F10" s="24" t="inlineStr"/>
       <c r="G10" s="24" t="inlineStr"/>
-      <c r="H10" s="24" t="inlineStr"/>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="24" t="inlineStr"/>
       <c r="J10" s="24" t="inlineStr"/>
       <c r="K10" s="24" t="inlineStr"/>
@@ -1985,7 +2005,11 @@
       <c r="E11" s="24" t="inlineStr"/>
       <c r="F11" s="24" t="inlineStr"/>
       <c r="G11" s="24" t="inlineStr"/>
-      <c r="H11" s="24" t="inlineStr"/>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="24" t="inlineStr"/>
       <c r="J11" s="24" t="inlineStr"/>
       <c r="K11" s="24" t="inlineStr"/>
@@ -2026,7 +2050,11 @@
       <c r="E12" s="24" t="inlineStr"/>
       <c r="F12" s="24" t="inlineStr"/>
       <c r="G12" s="24" t="inlineStr"/>
-      <c r="H12" s="24" t="inlineStr"/>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I12" s="24" t="inlineStr"/>
       <c r="J12" s="24" t="inlineStr"/>
       <c r="K12" s="24" t="inlineStr"/>
@@ -2067,7 +2095,11 @@
       <c r="E13" s="25" t="inlineStr"/>
       <c r="F13" s="25" t="inlineStr"/>
       <c r="G13" s="25" t="inlineStr"/>
-      <c r="H13" s="25" t="inlineStr"/>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I13" s="25" t="inlineStr"/>
       <c r="J13" s="25" t="inlineStr"/>
       <c r="K13" s="25" t="inlineStr"/>
@@ -2108,7 +2140,11 @@
       <c r="E14" s="25" t="inlineStr"/>
       <c r="F14" s="25" t="inlineStr"/>
       <c r="G14" s="25" t="inlineStr"/>
-      <c r="H14" s="25" t="inlineStr"/>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I14" s="25" t="inlineStr"/>
       <c r="J14" s="25" t="inlineStr"/>
       <c r="K14" s="25" t="inlineStr"/>
@@ -2149,7 +2185,11 @@
       <c r="E15" s="25" t="inlineStr"/>
       <c r="F15" s="25" t="inlineStr"/>
       <c r="G15" s="25" t="inlineStr"/>
-      <c r="H15" s="25" t="inlineStr"/>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I15" s="25" t="inlineStr"/>
       <c r="J15" s="25" t="inlineStr"/>
       <c r="K15" s="25" t="inlineStr"/>
@@ -2190,7 +2230,11 @@
       <c r="E16" s="25" t="inlineStr"/>
       <c r="F16" s="25" t="inlineStr"/>
       <c r="G16" s="25" t="inlineStr"/>
-      <c r="H16" s="25" t="inlineStr"/>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I16" s="25" t="inlineStr"/>
       <c r="J16" s="25" t="inlineStr"/>
       <c r="K16" s="25" t="inlineStr"/>
@@ -2225,7 +2269,11 @@
       <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="9" t="inlineStr"/>
       <c r="G17" s="9" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr"/>
+      <c r="H17" s="39" t="inlineStr">
+        <is>
+          <t>พีรวิชญ์ เนียมชุ่มรัตน์</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="inlineStr"/>
       <c r="J17" s="9" t="inlineStr"/>
       <c r="K17" s="9" t="inlineStr"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -1785,7 +1785,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr"/>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="24" t="inlineStr"/>
       <c r="K6" s="24" t="inlineStr"/>
       <c r="L6" s="24" t="inlineStr"/>
@@ -1830,7 +1834,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr"/>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="24" t="inlineStr"/>
       <c r="K7" s="24" t="inlineStr"/>
       <c r="L7" s="24" t="inlineStr"/>
@@ -1875,7 +1883,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr"/>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="24" t="inlineStr"/>
       <c r="K8" s="24" t="inlineStr"/>
       <c r="L8" s="24" t="inlineStr"/>
@@ -1920,7 +1932,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr"/>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="24" t="inlineStr"/>
       <c r="K9" s="24" t="inlineStr"/>
       <c r="L9" s="24" t="inlineStr"/>
@@ -1965,7 +1981,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr"/>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="24" t="inlineStr"/>
       <c r="K10" s="24" t="inlineStr"/>
       <c r="L10" s="24" t="inlineStr"/>
@@ -2010,7 +2030,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr"/>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="24" t="inlineStr"/>
       <c r="K11" s="24" t="inlineStr"/>
       <c r="L11" s="24" t="inlineStr"/>
@@ -2055,7 +2079,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr"/>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="24" t="inlineStr"/>
       <c r="K12" s="24" t="inlineStr"/>
       <c r="L12" s="24" t="inlineStr"/>
@@ -2100,7 +2128,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr"/>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J13" s="25" t="inlineStr"/>
       <c r="K13" s="25" t="inlineStr"/>
       <c r="L13" s="25" t="inlineStr"/>
@@ -2145,7 +2177,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr"/>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J14" s="25" t="inlineStr"/>
       <c r="K14" s="25" t="inlineStr"/>
       <c r="L14" s="25" t="inlineStr"/>
@@ -2190,7 +2226,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr"/>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J15" s="25" t="inlineStr"/>
       <c r="K15" s="25" t="inlineStr"/>
       <c r="L15" s="25" t="inlineStr"/>
@@ -2235,7 +2275,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr"/>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J16" s="25" t="inlineStr"/>
       <c r="K16" s="25" t="inlineStr"/>
       <c r="L16" s="25" t="inlineStr"/>
@@ -2274,7 +2318,11 @@
           <t>พีรวิชญ์ เนียมชุ่มรัตน์</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr"/>
+      <c r="I17" s="39" t="inlineStr">
+        <is>
+          <t>พีรวิชญ์ เนียมชุ่มรัตน์</t>
+        </is>
+      </c>
       <c r="J17" s="9" t="inlineStr"/>
       <c r="K17" s="9" t="inlineStr"/>
       <c r="L17" s="9" t="inlineStr"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -1790,7 +1790,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr"/>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="24" t="inlineStr"/>
       <c r="L6" s="24" t="inlineStr"/>
       <c r="M6" s="24" t="inlineStr"/>
@@ -1839,7 +1843,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="24" t="inlineStr"/>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="24" t="inlineStr"/>
       <c r="L7" s="24" t="inlineStr"/>
       <c r="M7" s="24" t="inlineStr"/>
@@ -1888,7 +1896,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="24" t="inlineStr"/>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="24" t="inlineStr"/>
       <c r="L8" s="24" t="inlineStr"/>
       <c r="M8" s="24" t="inlineStr"/>
@@ -1937,7 +1949,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="24" t="inlineStr"/>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="24" t="inlineStr"/>
       <c r="L9" s="24" t="inlineStr"/>
       <c r="M9" s="24" t="inlineStr"/>
@@ -1986,7 +2002,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="24" t="inlineStr"/>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="24" t="inlineStr"/>
       <c r="L10" s="24" t="inlineStr"/>
       <c r="M10" s="24" t="inlineStr"/>
@@ -2035,7 +2055,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="24" t="inlineStr"/>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="24" t="inlineStr"/>
       <c r="L11" s="24" t="inlineStr"/>
       <c r="M11" s="24" t="inlineStr"/>
@@ -2084,7 +2108,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J12" s="24" t="inlineStr"/>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K12" s="24" t="inlineStr"/>
       <c r="L12" s="24" t="inlineStr"/>
       <c r="M12" s="24" t="inlineStr"/>
@@ -2133,7 +2161,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J13" s="25" t="inlineStr"/>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K13" s="25" t="inlineStr"/>
       <c r="L13" s="25" t="inlineStr"/>
       <c r="M13" s="25" t="inlineStr"/>
@@ -2182,7 +2214,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J14" s="25" t="inlineStr"/>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K14" s="25" t="inlineStr"/>
       <c r="L14" s="25" t="inlineStr"/>
       <c r="M14" s="25" t="inlineStr"/>
@@ -2231,7 +2267,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J15" s="25" t="inlineStr"/>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K15" s="25" t="inlineStr"/>
       <c r="L15" s="25" t="inlineStr"/>
       <c r="M15" s="25" t="inlineStr"/>
@@ -2280,7 +2320,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr"/>
+      <c r="J16" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K16" s="25" t="inlineStr"/>
       <c r="L16" s="25" t="inlineStr"/>
       <c r="M16" s="25" t="inlineStr"/>
@@ -2428,7 +2472,11 @@
       <c r="G20" s="29" t="n"/>
       <c r="H20" s="29" t="n"/>
       <c r="I20" s="29" t="n"/>
-      <c r="J20" s="29" t="n"/>
+      <c r="J20" s="39" t="inlineStr">
+        <is>
+          <t>พีรวิชญ์</t>
+        </is>
+      </c>
       <c r="K20" s="29" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>

--- a/FM-MN-07_MILLING-03.xlsx
+++ b/FM-MN-07_MILLING-03.xlsx
@@ -1796,7 +1796,11 @@
         </is>
       </c>
       <c r="K6" s="24" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="24" t="inlineStr"/>
       <c r="N6" s="24" t="inlineStr"/>
       <c r="O6" s="24" t="inlineStr"/>
@@ -1849,7 +1853,11 @@
         </is>
       </c>
       <c r="K7" s="24" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr"/>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="24" t="inlineStr"/>
       <c r="N7" s="24" t="inlineStr"/>
       <c r="O7" s="24" t="inlineStr"/>
@@ -1902,7 +1910,11 @@
         </is>
       </c>
       <c r="K8" s="24" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr"/>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="24" t="inlineStr"/>
       <c r="N8" s="24" t="inlineStr"/>
       <c r="O8" s="24" t="inlineStr"/>
@@ -1955,7 +1967,11 @@
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr"/>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="24" t="inlineStr"/>
       <c r="N9" s="24" t="inlineStr"/>
       <c r="O9" s="24" t="inlineStr"/>
@@ -2008,7 +2024,11 @@
         </is>
       </c>
       <c r="K10" s="24" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr"/>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="24" t="inlineStr"/>
       <c r="N10" s="24" t="inlineStr"/>
       <c r="O10" s="24" t="inlineStr"/>
@@ -2061,7 +2081,11 @@
         </is>
       </c>
       <c r="K11" s="24" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr"/>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="24" t="inlineStr"/>
       <c r="N11" s="24" t="inlineStr"/>
       <c r="O11" s="24" t="inlineStr"/>
@@ -2114,7 +2138,11 @@
         </is>
       </c>
       <c r="K12" s="24" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr"/>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M12" s="24" t="inlineStr"/>
       <c r="N12" s="24" t="inlineStr"/>
       <c r="O12" s="24" t="inlineStr"/>
@@ -2167,7 +2195,11 @@
         </is>
       </c>
       <c r="K13" s="25" t="inlineStr"/>
-      <c r="L13" s="25" t="inlineStr"/>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M13" s="25" t="inlineStr"/>
       <c r="N13" s="25" t="inlineStr"/>
       <c r="O13" s="25" t="inlineStr"/>
@@ -2220,7 +2252,11 @@
         </is>
       </c>
       <c r="K14" s="25" t="inlineStr"/>
-      <c r="L14" s="25" t="inlineStr"/>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M14" s="25" t="inlineStr"/>
       <c r="N14" s="25" t="inlineStr"/>
       <c r="O14" s="25" t="inlineStr"/>
@@ -2273,7 +2309,11 @@
         </is>
       </c>
       <c r="K15" s="25" t="inlineStr"/>
-      <c r="L15" s="25" t="inlineStr"/>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M15" s="25" t="inlineStr"/>
       <c r="N15" s="25" t="inlineStr"/>
       <c r="O15" s="25" t="inlineStr"/>
@@ -2326,7 +2366,11 @@
         </is>
       </c>
       <c r="K16" s="25" t="inlineStr"/>
-      <c r="L16" s="25" t="inlineStr"/>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M16" s="25" t="inlineStr"/>
       <c r="N16" s="25" t="inlineStr"/>
       <c r="O16" s="25" t="inlineStr"/>
@@ -2478,7 +2522,11 @@
         </is>
       </c>
       <c r="K20" s="29" t="n"/>
-      <c r="L20" s="29" t="n"/>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>พีรวิชญ์</t>
+        </is>
+      </c>
       <c r="M20" s="29" t="n"/>
       <c r="N20" s="29" t="n"/>
       <c r="O20" s="29" t="n"/>
